--- a/astro-site/public/dl/kit-tareas-heladeria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-heladeria/05-tareas-semanales-mensuales.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Limpieza Semanal" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Gestión Semanal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Tareas Mensuales" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Limpieza Semanal" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gestión Semanal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tareas Mensuales" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Limpieza Semanal'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Gestión Semanal'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Tareas Mensuales'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,6 +85,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="10">
@@ -163,63 +172,74 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="8" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="9" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -579,15 +599,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -595,6 +616,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -623,9 +645,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -647,8 +667,25 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-heladeria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -657,18 +694,18 @@
   <sheetPr>
     <tabColor rgb="00EFEBE9"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -685,6 +722,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -805,6 +843,7 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="13" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -944,6 +983,7 @@
       <c r="F17" s="11" t="n"/>
       <c r="G17" s="13" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
@@ -1044,6 +1084,26 @@
       <c r="E23" s="12" t="n"/>
       <c r="F23" s="11" t="n"/>
       <c r="G23" s="13" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C24">
+        <f>COUNTIF(E6:E23,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E24">
+        <f>COUNTIF(B6:B23,"?*")</f>
+        <v>14.0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
@@ -1069,12 +1129,26 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A26:G26"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G23">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17 E21 E22 E23" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17 E21 E22 E23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1083,18 +1157,18 @@
   <sheetPr>
     <tabColor rgb="00FFF8E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1111,6 +1185,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1231,6 +1306,7 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="13" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -1331,6 +1407,26 @@
       <c r="E15" s="12" t="n"/>
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="13" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>COUNTIF(E6:E15,"✓")</f>
+        <v>1.0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E16">
+        <f>COUNTIF(B6:B15,"?*")</f>
+        <v>8.0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
@@ -1355,12 +1451,26 @@
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G15">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E13 E14 E15" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1369,18 +1479,18 @@
   <sheetPr>
     <tabColor rgb="00FFF8E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1397,6 +1507,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1517,6 +1628,7 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="13" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -1618,6 +1730,7 @@
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="13" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -1756,6 +1869,26 @@
       <c r="E23" s="12" t="n"/>
       <c r="F23" s="11" t="n"/>
       <c r="G23" s="13" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C24">
+        <f>COUNTIF(E6:E23,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E24">
+        <f>COUNTIF(B6:B23,"?*")</f>
+        <v>14.0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
@@ -1781,11 +1914,25 @@
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A26:G26"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G23">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E22 E23" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E22 E23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-heladeria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-heladeria/05-tareas-semanales-mensuales.xlsx
@@ -11,11 +11,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Limpieza Semanal" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gestión Semanal" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tareas Mensuales" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trimestral y Anual" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Limpieza Semanal'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Gestión Semanal'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Tareas Mensuales'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Trimestral y Anual'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -601,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -669,9 +671,45 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-heladeria · info@aichef.pro</t>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Lo que no es semanal ni mensual:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>▸ La hoja «Trimestral y Anual» recoge lo que se contrata fuera y lo que pide una inspección: DDD, conductos de extracción, gases fluorados, calibración de sondas, extintores, gas, legionela, registro sanitario, formación en alérgenos, póliza y facturación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>▸ En esa hoja la columna «Cadencia» sustituye a «Hora», y el número de parte del mantenedor se anota en «Notas»: sin el parte firmado, la tarea no está hecha a efectos de inspección.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>▸ La cobertura de pérdida de mercancía por avería del frío no es un extra en una heladería: es la que responde cuando una cámara se para en agosto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-heladeria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -1092,8 +1130,8 @@
         </is>
       </c>
       <c r="C24">
-        <f>COUNTIF(E6:E23,"✓")</f>
-        <v>2.0</v>
+        <f>COUNTIFS(B6:B23,"?*",E6:E23,"✓")-COUNTIFS(B6:B23,"Tarea",E6:E23,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1101,8 +1139,8 @@
         </is>
       </c>
       <c r="E24">
-        <f>COUNTIF(B6:B23,"?*")</f>
-        <v>14.0</v>
+        <f>COUNTIF(B6:B23,"?*")-COUNTIF(B6:B23,"Tarea")-COUNTIF(E6:E23,"N/A")</f>
+        <v>12.0</v>
       </c>
     </row>
     <row r="25">
@@ -1135,8 +1173,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17 E21 E22 E23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17 E21 E22 E23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1159,7 +1197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1306,82 +1344,82 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="13" t="n"/>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Si sirves café o bebidas calientes: backflush del grupo con detergente, cambio de junta si toca y ciclo de limpieza del lavavajillas (filtros y brazos de lavado)</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="13" t="n"/>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Inventario y rotación</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Inventario rápido de materias primas clave</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>Almacén</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="13" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Verificar rotación de sabores en vitrina (retirar poco demandados)</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Vitrina</t>
+          <t>Inventario rápido de materias primas clave</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Almacén</t>
         </is>
       </c>
       <c r="D14" s="11" t="n"/>
@@ -1391,16 +1429,16 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Comprobar stock de envases y material de servicio</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>Almacén</t>
+          <t>Verificar rotación de sabores en vitrina (retirar poco demandados)</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
         </is>
       </c>
       <c r="D15" s="11" t="n"/>
@@ -1409,34 +1447,53 @@
       <c r="G15" s="13" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="21" t="inlineStr">
+      <c r="A16" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Comprobar stock de envases y material de servicio</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Almacén</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C16">
-        <f>COUNTIF(E6:E15,"✓")</f>
-        <v>1.0</v>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17">
+        <f>COUNTIFS(B6:B16,"?*",E6:E16,"✓")-COUNTIFS(B6:B16,"Tarea",E6:E16,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E16">
-        <f>COUNTIF(B6:B15,"?*")</f>
+      <c r="E17">
+        <f>COUNTIF(B6:B16,"?*")-COUNTIF(B6:B16,"Tarea")-COUNTIF(E6:E16,"N/A")</f>
         <v>8.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
@@ -1445,20 +1502,20 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A19:G19"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G15">
+  <conditionalFormatting sqref="A6:G16">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1877,8 +1934,8 @@
         </is>
       </c>
       <c r="C24">
-        <f>COUNTIF(E6:E23,"✓")</f>
-        <v>2.0</v>
+        <f>COUNTIFS(B6:B23,"?*",E6:E23,"✓")-COUNTIFS(B6:B23,"Tarea",E6:E23,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1886,8 +1943,8 @@
         </is>
       </c>
       <c r="E24">
-        <f>COUNTIF(B6:B23,"?*")</f>
-        <v>14.0</v>
+        <f>COUNTIF(B6:B23,"?*")-COUNTIF(B6:B23,"Tarea")-COUNTIF(E6:E23,"N/A")</f>
+        <v>12.0</v>
       </c>
     </row>
     <row r="25">
@@ -1920,8 +1977,519 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E22 E23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E22 E23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFF8E1"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Mantenimiento Trimestral y Anual — Heladería Artesanal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>AI Chef Pro · aichef.pro — Kit de Tareas: Heladería Artesanal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Trimestral — control por empresa externa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Servicio de DDD (desinsectación y desratización) por empresa inscrita en el registro oficial: exige el parte firmado y anota su nº en «Notas»</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Limpieza de la campana y de los conductos de extracción del obrador por empresa autorizada, con certificado</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de la instalación frigorífica y control de fugas de gases fluorados (Rgto. UE 517/2014), con anotación en el libro del equipo</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Cámara</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Calibración externa de sondas y termómetros de vitrinas, cámaras y pasteurizador, con certificado: sin calibrar, el registro de temperaturas no prueba nada</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="n"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Anual — seguridad de las instalaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Revisión anual de extintores y BIE por empresa autorizada (y retimbrado del extintor cada 5 años): guarda el parte</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de la instalación de gas si la hay (gofrera, crepera, agua caliente) y de la instalación eléctrica según la periodicidad que te corresponda</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Prevención de legionela si tienes agua caliente sanitaria de riesgo o nebulizadores de terraza: plan, tratamiento y registro</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="n"/>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Anual — documentación, seguros y sistemas</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Comprobar que el registro sanitario del establecimiento sigue vigente y que los datos que constan son los actuales</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Revisar la formación en manipulación de alimentos y en alérgenos de TODA la plantilla, refuerzo de verano incluido</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Renovar la póliza y revisar coberturas, en especial la de pérdida de mercancía por avería del frío: una cámara parada en agosto se lleva la temporada entera</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Revisar con tu asesoría el TPV y el sistema de facturación verificable antes del cierre del ejercicio</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Archivar los registros de temperatura y limpieza del año y revisar el plan de autocontrol si has cambiado equipos, recetas o proveedores</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C24">
+        <f>COUNTIFS(B6:B23,"?*",E6:E23,"✓")-COUNTIFS(B6:B23,"Tarea",E6:E23,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E24">
+        <f>COUNTIF(B6:B23,"?*")-COUNTIF(B6:B23,"Tarea")-COUNTIF(E6:E23,"N/A")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>© 2026 AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A26:G26"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A6:G23">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E22 E23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-heladeria/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-heladeria/05-tareas-semanales-mensuales.xlsx
@@ -603,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
